--- a/Demo/CES/demo_ces_9999_2_couverture.xlsx
+++ b/Demo/CES/demo_ces_9999_2_couverture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\CES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769DD9DF-1E1A-4826-9A3F-2161F6B52BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1410BD03-31F7-4802-9D8E-EECE03F2707A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{D652F864-A1F2-4548-8BEB-05406EF57254}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{D652F864-A1F2-4548-8BEB-05406EF57254}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="609">
   <si>
     <t>type</t>
   </si>
@@ -1685,9 +1685,6 @@
     <t>Did the doctor take your height before giving you the medication?</t>
   </si>
   <si>
-    <t>${p_received_ivm} = 'Yes' or  ${p_received_alb} != 'Yes' or  ${p_received_mbz} != 'Yes' or  ${p_received_pzq} != 'Yes' or  ${p_received_dec} != 'Yes' or  ${p_received_tetra} != 'Yes' or  ${p_received_az_tab} != 'Yes' or  ${p_received_az_susp} != 'Yes'</t>
-  </si>
-  <si>
     <t>Did you experience any side effects after taking medicine?</t>
   </si>
   <si>
@@ -1847,9 +1844,6 @@
     <t>selected(${p_nt_reason_never_swallowed_az_tab}, 'Other')</t>
   </si>
   <si>
-    <t>(${p_received_ivm} = 'Yes' or  ${p_received_alb} != 'Yes' or  ${p_received_mbz} != 'Yes' or  ${p_received_pzq} != 'Yes' or  ${p_received_dec} != 'Yes' or  ${p_received_tetra} != 'Yes' or  ${p_received_az_tab} != 'Yes' or  ${p_received_az_susp} != 'Yes')  and (${p_respondent} = 'Lui_meme' or ${p_respondent} = 'Pour_enfant_present')</t>
-  </si>
-  <si>
     <t>selected(${p_nt_reason_never_swallowed_mbz}, 'Other')</t>
   </si>
   <si>
@@ -1857,17 +1851,36 @@
   </si>
   <si>
     <t>(Demo) CES - 2. Formulaire Couverture</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>${p_site_id}</t>
+  </si>
+  <si>
+    <t>${p_received_ivm} = 'Yes' or  ${p_received_alb} = 'Yes' or  ${p_received_mbz} = 'Yes' or  ${p_received_pzq} = 'Yes' or  ${p_received_dec} = 'Yes' or  ${p_received_tetra} = 'Yes' or  ${p_received_az_tab} = 'Yes' or  ${p_received_az_susp} = 'Yes'</t>
+  </si>
+  <si>
+    <t>(${p_received_ivm} = 'Yes' or  ${p_received_alb} = 'Yes' or  ${p_received_mbz} = 'Yes' or  ${p_received_pzq} = 'Yes' or  ${p_received_dec} = 'Yes' or  ${p_received_tetra} = 'Yes' or  ${p_received_az_tab} = 'Yes' or  ${p_received_az_susp} = 'Yes')  and (${p_respondent} = 'Lui_meme' or ${p_respondent} = 'Pour_enfant_present')</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1944,6 +1957,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -2012,75 +2032,79 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2409,7 +2433,8 @@
     <col min="4" max="4" width="23.7109375" style="7" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" style="7" customWidth="1"/>
     <col min="6" max="6" width="36.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="17" style="7" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="17" style="7" customWidth="1"/>
     <col min="9" max="9" width="24.7109375" style="7" customWidth="1"/>
     <col min="10" max="10" width="13.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="22" style="7" bestFit="1" customWidth="1"/>
@@ -2481,7 +2506,7 @@
         <v>52</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C2" s="23" t="s">
         <v>95</v>
@@ -2608,7 +2633,7 @@
       <c r="A6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="44" t="s">
         <v>83</v>
       </c>
       <c r="C6" s="28" t="s">
@@ -2658,7 +2683,7 @@
       <c r="Q7" s="24"/>
       <c r="R7" s="32"/>
     </row>
-    <row r="8" spans="1:21" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" s="8" customFormat="1" ht="30" x14ac:dyDescent="0.35">
       <c r="A8" s="22" t="s">
         <v>53</v>
       </c>
@@ -2687,8 +2712,12 @@
       <c r="N8" s="32"/>
       <c r="O8" s="24"/>
       <c r="P8" s="35"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="32"/>
+      <c r="Q8" s="24" t="s">
+        <v>606</v>
+      </c>
+      <c r="R8" s="43" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="9" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32"/>
@@ -3111,7 +3140,7 @@
         <v>314</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C23" s="23" t="s">
         <v>426</v>
@@ -3141,7 +3170,7 @@
         <v>9</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C24" s="23" t="s">
         <v>427</v>
@@ -3150,7 +3179,7 @@
       <c r="E24" s="32"/>
       <c r="F24" s="25"/>
       <c r="G24" s="32" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H24" s="32"/>
       <c r="I24" s="22" t="s">
@@ -3288,7 +3317,7 @@
     </row>
     <row r="29" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B29" s="22" t="s">
         <v>323</v>
@@ -3328,7 +3357,7 @@
       <c r="E30" s="32"/>
       <c r="F30" s="25"/>
       <c r="G30" s="32" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H30" s="32"/>
       <c r="I30" s="22" t="s">
@@ -3537,7 +3566,7 @@
         <v>314</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C38" s="23" t="s">
         <v>496</v>
@@ -3567,7 +3596,7 @@
         <v>9</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C39" s="23" t="s">
         <v>427</v>
@@ -3576,7 +3605,7 @@
       <c r="E39" s="32"/>
       <c r="F39" s="25"/>
       <c r="G39" s="32" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H39" s="32"/>
       <c r="I39" s="22" t="s">
@@ -3714,7 +3743,7 @@
     </row>
     <row r="44" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B44" s="22" t="s">
         <v>347</v>
@@ -3754,7 +3783,7 @@
       <c r="E45" s="32"/>
       <c r="F45" s="25"/>
       <c r="G45" s="32" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H45" s="32"/>
       <c r="I45" s="22" t="s">
@@ -3963,7 +3992,7 @@
         <v>314</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C53" s="23" t="s">
         <v>505</v>
@@ -3993,7 +4022,7 @@
         <v>9</v>
       </c>
       <c r="B54" s="22" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C54" s="23" t="s">
         <v>427</v>
@@ -4002,7 +4031,7 @@
       <c r="E54" s="32"/>
       <c r="F54" s="25"/>
       <c r="G54" s="32" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H54" s="32"/>
       <c r="I54" s="22" t="s">
@@ -4140,7 +4169,7 @@
     </row>
     <row r="59" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B59" s="22" t="s">
         <v>359</v>
@@ -4180,7 +4209,7 @@
       <c r="E60" s="32"/>
       <c r="F60" s="25"/>
       <c r="G60" s="32" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H60" s="32"/>
       <c r="I60" s="22" t="s">
@@ -4240,7 +4269,7 @@
       <c r="E62" s="32"/>
       <c r="F62" s="25"/>
       <c r="G62" s="32" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H62" s="32"/>
       <c r="I62" s="22" t="s">
@@ -4389,7 +4418,7 @@
         <v>314</v>
       </c>
       <c r="B68" s="22" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C68" s="23" t="s">
         <v>514</v>
@@ -4419,7 +4448,7 @@
         <v>9</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C69" s="23" t="s">
         <v>427</v>
@@ -4428,7 +4457,7 @@
       <c r="E69" s="32"/>
       <c r="F69" s="25"/>
       <c r="G69" s="32" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H69" s="32"/>
       <c r="I69" s="22" t="s">
@@ -4566,7 +4595,7 @@
     </row>
     <row r="74" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B74" s="22" t="s">
         <v>371</v>
@@ -4606,7 +4635,7 @@
       <c r="E75" s="32"/>
       <c r="F75" s="25"/>
       <c r="G75" s="32" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H75" s="32"/>
       <c r="I75" s="22" t="s">
@@ -4815,7 +4844,7 @@
         <v>314</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C83" s="23" t="s">
         <v>523</v>
@@ -4845,7 +4874,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C84" s="23" t="s">
         <v>427</v>
@@ -4854,7 +4883,7 @@
       <c r="E84" s="32"/>
       <c r="F84" s="25"/>
       <c r="G84" s="32" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H84" s="32"/>
       <c r="I84" s="22" t="s">
@@ -4992,7 +5021,7 @@
     </row>
     <row r="89" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B89" s="22" t="s">
         <v>383</v>
@@ -5032,7 +5061,7 @@
       <c r="E90" s="32"/>
       <c r="F90" s="25"/>
       <c r="G90" s="32" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H90" s="32"/>
       <c r="I90" s="22" t="s">
@@ -5241,7 +5270,7 @@
         <v>314</v>
       </c>
       <c r="B98" s="22" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C98" s="23" t="s">
         <v>532</v>
@@ -5271,7 +5300,7 @@
         <v>9</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C99" s="23" t="s">
         <v>427</v>
@@ -5280,7 +5309,7 @@
       <c r="E99" s="32"/>
       <c r="F99" s="25"/>
       <c r="G99" s="32" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H99" s="32"/>
       <c r="I99" s="22" t="s">
@@ -5418,7 +5447,7 @@
     </row>
     <row r="104" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B104" s="22" t="s">
         <v>395</v>
@@ -5458,7 +5487,7 @@
       <c r="E105" s="32"/>
       <c r="F105" s="25"/>
       <c r="G105" s="32" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H105" s="32"/>
       <c r="I105" s="22" t="s">
@@ -5667,7 +5696,7 @@
         <v>314</v>
       </c>
       <c r="B113" s="22" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C113" s="23" t="s">
         <v>541</v>
@@ -5697,7 +5726,7 @@
         <v>9</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C114" s="23" t="s">
         <v>427</v>
@@ -5706,7 +5735,7 @@
       <c r="E114" s="32"/>
       <c r="F114" s="25"/>
       <c r="G114" s="32" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H114" s="32"/>
       <c r="I114" s="22" t="s">
@@ -5844,7 +5873,7 @@
     </row>
     <row r="119" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B119" s="22" t="s">
         <v>407</v>
@@ -5884,7 +5913,7 @@
       <c r="E120" s="32"/>
       <c r="F120" s="25"/>
       <c r="G120" s="32" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H120" s="32"/>
       <c r="I120" s="22" t="s">
@@ -5944,7 +5973,7 @@
       <c r="E122" s="32"/>
       <c r="F122" s="25"/>
       <c r="G122" s="32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H122" s="32"/>
       <c r="I122" s="22" t="s">
@@ -6007,7 +6036,7 @@
         <v>276</v>
       </c>
       <c r="B125" s="40" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C125" s="40" t="s">
         <v>397</v>
@@ -6093,7 +6122,7 @@
         <v>314</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C128" s="23" t="s">
         <v>541</v>
@@ -6123,7 +6152,7 @@
         <v>9</v>
       </c>
       <c r="B129" s="22" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C129" s="23" t="s">
         <v>427</v>
@@ -6132,7 +6161,7 @@
       <c r="E129" s="32"/>
       <c r="F129" s="25"/>
       <c r="G129" s="32" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H129" s="32"/>
       <c r="I129" s="22" t="s">
@@ -6270,7 +6299,7 @@
     </row>
     <row r="134" spans="1:18" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B134" s="22" t="s">
         <v>417</v>
@@ -6310,7 +6339,7 @@
       <c r="E135" s="32"/>
       <c r="F135" s="25"/>
       <c r="G135" s="32" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H135" s="32"/>
       <c r="I135" s="22" t="s">
@@ -6422,7 +6451,7 @@
       <c r="E139" s="32"/>
       <c r="F139" s="25"/>
       <c r="G139" s="32" t="s">
-        <v>549</v>
+        <v>607</v>
       </c>
       <c r="H139" s="32"/>
       <c r="I139" s="22" t="s">
@@ -6446,13 +6475,13 @@
         <v>134</v>
       </c>
       <c r="C140" s="23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D140" s="23"/>
       <c r="E140" s="32"/>
       <c r="F140" s="25"/>
       <c r="G140" s="32" t="s">
-        <v>549</v>
+        <v>607</v>
       </c>
       <c r="H140" s="32"/>
       <c r="I140" s="22" t="s">
@@ -6476,13 +6505,13 @@
         <v>135</v>
       </c>
       <c r="C141" s="23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="D141" s="23"/>
       <c r="E141" s="32"/>
       <c r="F141" s="25"/>
       <c r="G141" s="32" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="H141" s="32"/>
       <c r="I141" s="22" t="s">
@@ -6506,13 +6535,13 @@
         <v>136</v>
       </c>
       <c r="C142" s="23" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D142" s="23"/>
       <c r="E142" s="32"/>
       <c r="F142" s="25"/>
       <c r="G142" s="22" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H142" s="32"/>
       <c r="I142" s="22" t="s">
@@ -6536,13 +6565,13 @@
         <v>137</v>
       </c>
       <c r="C143" s="23" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D143" s="23"/>
       <c r="E143" s="32"/>
       <c r="F143" s="25"/>
       <c r="G143" s="22" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H143" s="32"/>
       <c r="I143" s="22" t="s">
@@ -6566,7 +6595,7 @@
         <v>138</v>
       </c>
       <c r="C144" s="23" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D144" s="23"/>
       <c r="E144" s="32"/>
@@ -6596,13 +6625,13 @@
         <v>139</v>
       </c>
       <c r="C145" s="23" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D145" s="23"/>
       <c r="E145" s="32"/>
       <c r="F145" s="25"/>
       <c r="G145" s="22" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H145" s="32"/>
       <c r="I145" s="22" t="s">
@@ -6626,13 +6655,13 @@
         <v>140</v>
       </c>
       <c r="C146" s="23" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D146" s="23"/>
       <c r="E146" s="32"/>
       <c r="F146" s="25"/>
       <c r="G146" s="22" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H146" s="32"/>
       <c r="I146" s="22" t="s">
@@ -6656,7 +6685,7 @@
         <v>141</v>
       </c>
       <c r="C147" s="23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D147" s="23"/>
       <c r="E147" s="32"/>
@@ -6684,13 +6713,13 @@
         <v>142</v>
       </c>
       <c r="C148" s="23" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D148" s="23"/>
       <c r="E148" s="32"/>
       <c r="F148" s="25"/>
       <c r="G148" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H148" s="32"/>
       <c r="I148" s="22" t="s">
@@ -6714,7 +6743,7 @@
         <v>49</v>
       </c>
       <c r="C149" s="23" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D149" s="23"/>
       <c r="E149" s="32"/>
@@ -6742,7 +6771,7 @@
         <v>143</v>
       </c>
       <c r="C150" s="23" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D150" s="23" t="s">
         <v>131</v>
@@ -6774,7 +6803,7 @@
         <v>144</v>
       </c>
       <c r="C151" s="23" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D151" s="23" t="s">
         <v>132</v>
@@ -6782,7 +6811,7 @@
       <c r="E151" s="32"/>
       <c r="F151" s="25"/>
       <c r="G151" s="22" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="H151" s="32"/>
       <c r="I151" s="22" t="s">
@@ -7542,7 +7571,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>284</v>
@@ -7553,7 +7582,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>282</v>
@@ -7564,7 +7593,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>283</v>
@@ -8153,7 +8182,7 @@
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>76</v>
